--- a/data/dados_aula_django_rest_framework.xlsx
+++ b/data/dados_aula_django_rest_framework.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\52275348883\Documents\aulas\PWBE\rent-system\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16C2AA6F-E814-436C-8F23-166F9DEEA504}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2395DE5B-7364-40CE-B14E-7618CC1423A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Roteiro" sheetId="1" r:id="rId1"/>
@@ -3170,7 +3170,7 @@
         <v>36</v>
       </c>
       <c r="F7">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="G7" t="s">
         <v>289</v>
@@ -3191,7 +3191,7 @@
         <v>37</v>
       </c>
       <c r="F8">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="G8" t="s">
         <v>290</v>
@@ -3214,7 +3214,7 @@
         <v>38</v>
       </c>
       <c r="F9">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="G9" t="s">
         <v>291</v>
@@ -3237,7 +3237,7 @@
         <v>31</v>
       </c>
       <c r="F10">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="G10" t="s">
         <v>292</v>
@@ -3260,7 +3260,7 @@
         <v>32</v>
       </c>
       <c r="F11">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="G11" t="s">
         <v>288</v>
@@ -3283,7 +3283,7 @@
         <v>33</v>
       </c>
       <c r="F12">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="G12" t="s">
         <v>284</v>
@@ -3306,7 +3306,7 @@
         <v>34</v>
       </c>
       <c r="F13">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="G13" t="s">
         <v>284</v>
@@ -3357,7 +3357,7 @@
         <v>1</v>
       </c>
       <c r="D2">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E2" t="s">
         <v>295</v>
@@ -3374,7 +3374,7 @@
         <v>1</v>
       </c>
       <c r="D3">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E3" t="s">
         <v>295</v>
@@ -3391,7 +3391,7 @@
         <v>0</v>
       </c>
       <c r="D4">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="E4" t="s">
         <v>296</v>
@@ -3408,7 +3408,7 @@
         <v>1</v>
       </c>
       <c r="D5">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="E5" t="s">
         <v>295</v>
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="D6">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E6" t="s">
         <v>296</v>
@@ -3442,7 +3442,7 @@
         <v>1</v>
       </c>
       <c r="D7">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E7" t="s">
         <v>295</v>
@@ -3459,7 +3459,7 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E8" t="s">
         <v>296</v>
